--- a/naive/deepseek/result.xlsx
+++ b/naive/deepseek/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,7 +915,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[[494, 560]]</t>
+          <t>[[294, 560]]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -927,23 +927,23 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.208955223880597</v>
+        <v>0.05243445692883895</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.345679012345679</v>
+        <v>0.09964412811387902</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>['PR#144453']</t>
+          <t>['PR#144459', 'PR#144453']</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -952,22 +952,22 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>['PR#7306']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1138,6 +1138,2046 @@
       </c>
       <c r="W8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>commander.js</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>169431</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[[140, 168]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[[140, 168]]</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>29</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>['PR#2333']</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{'pr1': 2333}</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>commander.js</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>169066</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[[124, 152]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[[124, 152]]</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>['PR#2333']</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{'pr1': 2333}</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>commander.js</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pair_3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>169454</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[[140, 168]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[[140, 168]]</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>29</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>['PR#2333']</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'pr1': 2334}</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dify</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>73971</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[[1148, 1182]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[[725, 1182]]</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>423</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.07641921397379912</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1419878296146045</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'pr1': 18047, 'pr2': 18035}</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>duckdb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>27336</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[[440, 511]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[[498, 511]]</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" t="n">
+        <v>58</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'pr1': 17109}</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fzf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>22461</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[[510, 535]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[[510, 535]]</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>['PR#4305', 'PR#4306']</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'pr1': 4307, 'pr2': 4306}</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>godot</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>24018</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[[332, 424]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[[332, 424]]</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>93</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>['PR#85767']</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'pr1': 105400}</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gpt_academic</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>140664</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[[963, 1390]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[[680, 1390]]</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>428</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>283</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6019690576652602</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7515364354697104</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'pr1': 2139}</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gpt_academic</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>96766</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[[962, 1226]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[[989, 1250]]</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>238</v>
+      </c>
+      <c r="K17" t="n">
+        <v>27</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8981132075471698</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9083969465648855</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'pr1': 2139, 'pr2': 2136}</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gpt_academic</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pair_3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>132214</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[[962, 1347]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[[680, 1347]]</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>386</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>282</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.5778443113772455</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.732447817836812</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gpt_academic</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pair_4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>96763</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[[972, 1234]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[[999, 1234]]</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>236</v>
+      </c>
+      <c r="K19" t="n">
+        <v>27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8973384030418251</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.9458917835671342</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'pr1': 2139}</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hugo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>264947</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[[5799, 6233]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[[5799, 6233]]</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>435</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hugo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>265420</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[[5980, 6246]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[[5812, 6246]]</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>267</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>168</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.6137931034482759</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7606837606837606</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>insomnia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>116650</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[[417, 496]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[[417, 496]]</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>80</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['PR#8610']</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'pr1': 8614, 'pr2': 8613}</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ionic-framework</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>53353</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[[215, 663]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[[500, 663]]</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>164</v>
+      </c>
+      <c r="K23" t="n">
+        <v>285</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3652561247216036</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5350734094616639</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>['PR#30353']</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'pr1': 30350}</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>jan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>152046</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[[1180, 1458]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[[785, 1458]]</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>279</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>395</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.413946587537092</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5855194123819517</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>['PR#4904']</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'pr1': 4904}</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LLMs-from-scratch</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>45305</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[[401, 475]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[[401, 475]]</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['PR#615']</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'pr1': 616, 'pr2': 615}</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>meilisearch</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>58499</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[[539, 559]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[[539, 559]]</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>21</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'pr1': 5509}</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>meilisearch</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pair_2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>59779</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[[539, 559]]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[[539, 559]]</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>21</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'pr1': 5509}</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>meilisearch</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pair_3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>193006</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[[2525, 2806]]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[[1176, 2806]]</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>282</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1349</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.1729000613120785</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.2948248823836905</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'pr1': 5509}</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mongoose</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8985</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[[161, 184]]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[[161, 184]]</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'pr1': 15343}</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>nvm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>17068</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[[216, 276]]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[[252, 274]]</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>23</v>
+      </c>
+      <c r="K30" t="n">
+        <v>38</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3770491803278688</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5476190476190476</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>['PR#3553']</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pixijs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>34900</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[[218, 298]]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[[238, 298]]</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>61</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.7530864197530864</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8591549295774648</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>['PR#11351']</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RxJava</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pair_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>32270</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[[117, 751]]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[[174, 751]]</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>578</v>
+      </c>
+      <c r="K32" t="n">
+        <v>57</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.9102362204724409</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9530090684253915</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>['PR#7833']</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'pr1': 7833, 'pr2': 7828}</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
   </sheetData>
